--- a/15-10-2026/PAT_Berth_Window.xlsx
+++ b/15-10-2026/PAT_Berth_Window.xlsx
@@ -22,7 +22,7 @@
     <numFmt numFmtId="166" formatCode="[$-409]dd-mmm-yyyy hh:mm"/>
     <numFmt numFmtId="167" formatCode="0.0"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -62,6 +62,11 @@
       <b val="1"/>
       <color rgb="0016324F"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -171,7 +176,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -230,7 +235,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -248,29 +253,30 @@
     <xf numFmtId="164" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -730,13 +736,13 @@
       <c r="C4" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D4" s="39" t="n">
+      <c r="D4" s="40" t="n">
         <v>46310.33333333334</v>
       </c>
-      <c r="E4" s="39" t="n">
+      <c r="E4" s="40" t="n">
         <v>46310.375</v>
       </c>
-      <c r="F4" s="39" t="n">
+      <c r="F4" s="40" t="n">
         <v>46311.66666666666</v>
       </c>
       <c r="G4" s="24">
@@ -768,13 +774,13 @@
       <c r="C5" s="23" t="n">
         <v>551</v>
       </c>
-      <c r="D5" s="39" t="n">
+      <c r="D5" s="40" t="n">
         <v>46311.875</v>
       </c>
-      <c r="E5" s="39" t="n">
+      <c r="E5" s="40" t="n">
         <v>46312.375</v>
       </c>
-      <c r="F5" s="39" t="n">
+      <c r="F5" s="40" t="n">
         <v>46313.66666666666</v>
       </c>
       <c r="G5" s="24">
@@ -806,13 +812,13 @@
       <c r="C6" s="23" t="n">
         <v>558</v>
       </c>
-      <c r="D6" s="39" t="n">
+      <c r="D6" s="40" t="n">
         <v>46314.75</v>
       </c>
-      <c r="E6" s="39" t="n">
+      <c r="E6" s="40" t="n">
         <v>46314.75</v>
       </c>
-      <c r="F6" s="39" t="n">
+      <c r="F6" s="40" t="n">
         <v>46316.45833333334</v>
       </c>
       <c r="G6" s="24">
@@ -844,13 +850,13 @@
       <c r="C7" s="23" t="n">
         <v>482</v>
       </c>
-      <c r="D7" s="39" t="n">
+      <c r="D7" s="40" t="n">
         <v>46310.04166666666</v>
       </c>
-      <c r="E7" s="39" t="n">
+      <c r="E7" s="40" t="n">
         <v>46310.25</v>
       </c>
-      <c r="F7" s="39" t="n">
+      <c r="F7" s="40" t="n">
         <v>46311.29166666666</v>
       </c>
       <c r="G7" s="24">
@@ -882,13 +888,13 @@
       <c r="C8" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D8" s="39" t="n">
+      <c r="D8" s="40" t="n">
         <v>46311.70833333334</v>
       </c>
-      <c r="E8" s="39" t="n">
+      <c r="E8" s="40" t="n">
         <v>46311.70833333334</v>
       </c>
-      <c r="F8" s="39" t="n">
+      <c r="F8" s="40" t="n">
         <v>46313.29166666666</v>
       </c>
       <c r="G8" s="24">
@@ -920,13 +926,13 @@
       <c r="C9" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D9" s="39" t="n">
+      <c r="D9" s="40" t="n">
         <v>46312.91666666666</v>
       </c>
-      <c r="E9" s="39" t="n">
+      <c r="E9" s="40" t="n">
         <v>46313.33333333334</v>
       </c>
-      <c r="F9" s="39" t="n">
+      <c r="F9" s="40" t="n">
         <v>46314.29166666666</v>
       </c>
       <c r="G9" s="24">
@@ -958,13 +964,13 @@
       <c r="C10" s="23" t="n">
         <v>565</v>
       </c>
-      <c r="D10" s="39" t="n">
+      <c r="D10" s="40" t="n">
         <v>46309.875</v>
       </c>
-      <c r="E10" s="39" t="n">
+      <c r="E10" s="40" t="n">
         <v>46310.29166666666</v>
       </c>
-      <c r="F10" s="39" t="n">
+      <c r="F10" s="40" t="n">
         <v>46311.625</v>
       </c>
       <c r="G10" s="24">
@@ -996,13 +1002,13 @@
       <c r="C11" s="23" t="n">
         <v>485</v>
       </c>
-      <c r="D11" s="39" t="n">
+      <c r="D11" s="40" t="n">
         <v>46312.08333333334</v>
       </c>
-      <c r="E11" s="39" t="n">
+      <c r="E11" s="40" t="n">
         <v>46312.33333333334</v>
       </c>
-      <c r="F11" s="39" t="n">
+      <c r="F11" s="40" t="n">
         <v>46313.29166666666</v>
       </c>
       <c r="G11" s="24">
@@ -1034,13 +1040,13 @@
       <c r="C12" s="23" t="n">
         <v>565</v>
       </c>
-      <c r="D12" s="39" t="n">
+      <c r="D12" s="40" t="n">
         <v>46313.25</v>
       </c>
-      <c r="E12" s="39" t="n">
+      <c r="E12" s="40" t="n">
         <v>46313.29166666666</v>
       </c>
-      <c r="F12" s="39" t="n">
+      <c r="F12" s="40" t="n">
         <v>46314.41666666666</v>
       </c>
       <c r="G12" s="24">
@@ -1072,13 +1078,13 @@
       <c r="C13" s="23" t="n">
         <v>470</v>
       </c>
-      <c r="D13" s="39" t="n">
+      <c r="D13" s="40" t="n">
         <v>46309.33333333334</v>
       </c>
-      <c r="E13" s="39" t="n">
+      <c r="E13" s="40" t="n">
         <v>46310.20833333334</v>
       </c>
-      <c r="F13" s="39" t="n">
+      <c r="F13" s="40" t="n">
         <v>46311.25</v>
       </c>
       <c r="G13" s="24">
@@ -1110,13 +1116,13 @@
       <c r="C14" s="23" t="n">
         <v>565</v>
       </c>
-      <c r="D14" s="39" t="n">
+      <c r="D14" s="40" t="n">
         <v>46311.04166666666</v>
       </c>
-      <c r="E14" s="39" t="n">
+      <c r="E14" s="40" t="n">
         <v>46311.29166666666</v>
       </c>
-      <c r="F14" s="39" t="n">
+      <c r="F14" s="40" t="n">
         <v>46312.625</v>
       </c>
       <c r="G14" s="24">
@@ -1148,13 +1154,13 @@
       <c r="C15" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D15" s="39" t="n">
+      <c r="D15" s="40" t="n">
         <v>46312.75</v>
       </c>
-      <c r="E15" s="39" t="n">
+      <c r="E15" s="40" t="n">
         <v>46312.75</v>
       </c>
-      <c r="F15" s="39" t="n">
+      <c r="F15" s="40" t="n">
         <v>46313.45833333334</v>
       </c>
       <c r="G15" s="24">
@@ -1186,13 +1192,13 @@
       <c r="C16" s="23" t="n">
         <v>485</v>
       </c>
-      <c r="D16" s="39" t="n">
+      <c r="D16" s="40" t="n">
         <v>46314.95833333334</v>
       </c>
-      <c r="E16" s="39" t="n">
+      <c r="E16" s="40" t="n">
         <v>46315.375</v>
       </c>
-      <c r="F16" s="39" t="n">
+      <c r="F16" s="40" t="n">
         <v>46316.33333333334</v>
       </c>
       <c r="G16" s="24">
@@ -1224,13 +1230,13 @@
       <c r="C17" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D17" s="39" t="n">
+      <c r="D17" s="40" t="n">
         <v>46308.625</v>
       </c>
-      <c r="E17" s="39" t="n">
+      <c r="E17" s="40" t="n">
         <v>46309.25</v>
       </c>
-      <c r="F17" s="39" t="n">
+      <c r="F17" s="40" t="n">
         <v>46311.25</v>
       </c>
       <c r="G17" s="24">
@@ -1262,13 +1268,13 @@
       <c r="C18" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D18" s="39" t="n">
+      <c r="D18" s="40" t="n">
         <v>46311.95833333334</v>
       </c>
-      <c r="E18" s="39" t="n">
+      <c r="E18" s="40" t="n">
         <v>46312.33333333334</v>
       </c>
-      <c r="F18" s="39" t="n">
+      <c r="F18" s="40" t="n">
         <v>46313.29166666666</v>
       </c>
       <c r="G18" s="24">
@@ -1300,13 +1306,13 @@
       <c r="C19" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D19" s="39" t="n">
+      <c r="D19" s="40" t="n">
         <v>46313.83333333334</v>
       </c>
-      <c r="E19" s="39" t="n">
+      <c r="E19" s="40" t="n">
         <v>46313.83333333334</v>
       </c>
-      <c r="F19" s="39" t="n">
+      <c r="F19" s="40" t="n">
         <v>46315.33333333334</v>
       </c>
       <c r="G19" s="24">
@@ -1407,10 +1413,10 @@
         </is>
       </c>
       <c r="C25" s="38" t="n"/>
-      <c r="D25" s="40" t="n">
+      <c r="D25" s="41" t="n">
         <v>46300</v>
       </c>
-      <c r="E25" s="40" t="n">
+      <c r="E25" s="41" t="n">
         <v>46315</v>
       </c>
       <c r="F25" s="16" t="inlineStr">

--- a/15-10-2026/PAT_Berth_Window.xlsx
+++ b/15-10-2026/PAT_Berth_Window.xlsx
@@ -244,6 +244,12 @@
     <xf numFmtId="167" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -264,12 +270,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>

--- a/15-10-2026/PAT_Berth_Window.xlsx
+++ b/15-10-2026/PAT_Berth_Window.xlsx
@@ -176,7 +176,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -270,6 +270,15 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -736,13 +745,13 @@
       <c r="C4" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D4" s="40" t="n">
+      <c r="D4" s="43" t="n">
         <v>46310.33333333334</v>
       </c>
-      <c r="E4" s="40" t="n">
+      <c r="E4" s="43" t="n">
         <v>46310.375</v>
       </c>
-      <c r="F4" s="40" t="n">
+      <c r="F4" s="43" t="n">
         <v>46311.66666666666</v>
       </c>
       <c r="G4" s="24">
@@ -774,13 +783,13 @@
       <c r="C5" s="23" t="n">
         <v>551</v>
       </c>
-      <c r="D5" s="40" t="n">
+      <c r="D5" s="43" t="n">
         <v>46311.875</v>
       </c>
-      <c r="E5" s="40" t="n">
+      <c r="E5" s="43" t="n">
         <v>46312.375</v>
       </c>
-      <c r="F5" s="40" t="n">
+      <c r="F5" s="43" t="n">
         <v>46313.66666666666</v>
       </c>
       <c r="G5" s="24">
@@ -812,13 +821,13 @@
       <c r="C6" s="23" t="n">
         <v>558</v>
       </c>
-      <c r="D6" s="40" t="n">
+      <c r="D6" s="43" t="n">
         <v>46314.75</v>
       </c>
-      <c r="E6" s="40" t="n">
+      <c r="E6" s="43" t="n">
         <v>46314.75</v>
       </c>
-      <c r="F6" s="40" t="n">
+      <c r="F6" s="43" t="n">
         <v>46316.45833333334</v>
       </c>
       <c r="G6" s="24">
@@ -850,13 +859,13 @@
       <c r="C7" s="23" t="n">
         <v>482</v>
       </c>
-      <c r="D7" s="40" t="n">
+      <c r="D7" s="43" t="n">
         <v>46310.04166666666</v>
       </c>
-      <c r="E7" s="40" t="n">
+      <c r="E7" s="43" t="n">
         <v>46310.25</v>
       </c>
-      <c r="F7" s="40" t="n">
+      <c r="F7" s="43" t="n">
         <v>46311.29166666666</v>
       </c>
       <c r="G7" s="24">
@@ -888,13 +897,13 @@
       <c r="C8" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D8" s="40" t="n">
+      <c r="D8" s="43" t="n">
         <v>46311.70833333334</v>
       </c>
-      <c r="E8" s="40" t="n">
+      <c r="E8" s="43" t="n">
         <v>46311.70833333334</v>
       </c>
-      <c r="F8" s="40" t="n">
+      <c r="F8" s="43" t="n">
         <v>46313.29166666666</v>
       </c>
       <c r="G8" s="24">
@@ -926,13 +935,13 @@
       <c r="C9" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D9" s="40" t="n">
+      <c r="D9" s="43" t="n">
         <v>46312.91666666666</v>
       </c>
-      <c r="E9" s="40" t="n">
+      <c r="E9" s="43" t="n">
         <v>46313.33333333334</v>
       </c>
-      <c r="F9" s="40" t="n">
+      <c r="F9" s="43" t="n">
         <v>46314.29166666666</v>
       </c>
       <c r="G9" s="24">
@@ -964,13 +973,13 @@
       <c r="C10" s="23" t="n">
         <v>565</v>
       </c>
-      <c r="D10" s="40" t="n">
+      <c r="D10" s="43" t="n">
         <v>46309.875</v>
       </c>
-      <c r="E10" s="40" t="n">
+      <c r="E10" s="43" t="n">
         <v>46310.29166666666</v>
       </c>
-      <c r="F10" s="40" t="n">
+      <c r="F10" s="43" t="n">
         <v>46311.625</v>
       </c>
       <c r="G10" s="24">
@@ -1002,13 +1011,13 @@
       <c r="C11" s="23" t="n">
         <v>485</v>
       </c>
-      <c r="D11" s="40" t="n">
+      <c r="D11" s="43" t="n">
         <v>46312.08333333334</v>
       </c>
-      <c r="E11" s="40" t="n">
+      <c r="E11" s="43" t="n">
         <v>46312.33333333334</v>
       </c>
-      <c r="F11" s="40" t="n">
+      <c r="F11" s="43" t="n">
         <v>46313.29166666666</v>
       </c>
       <c r="G11" s="24">
@@ -1040,13 +1049,13 @@
       <c r="C12" s="23" t="n">
         <v>565</v>
       </c>
-      <c r="D12" s="40" t="n">
+      <c r="D12" s="43" t="n">
         <v>46313.25</v>
       </c>
-      <c r="E12" s="40" t="n">
+      <c r="E12" s="43" t="n">
         <v>46313.29166666666</v>
       </c>
-      <c r="F12" s="40" t="n">
+      <c r="F12" s="43" t="n">
         <v>46314.41666666666</v>
       </c>
       <c r="G12" s="24">
@@ -1078,13 +1087,13 @@
       <c r="C13" s="23" t="n">
         <v>470</v>
       </c>
-      <c r="D13" s="40" t="n">
+      <c r="D13" s="43" t="n">
         <v>46309.33333333334</v>
       </c>
-      <c r="E13" s="40" t="n">
+      <c r="E13" s="43" t="n">
         <v>46310.20833333334</v>
       </c>
-      <c r="F13" s="40" t="n">
+      <c r="F13" s="43" t="n">
         <v>46311.25</v>
       </c>
       <c r="G13" s="24">
@@ -1116,13 +1125,13 @@
       <c r="C14" s="23" t="n">
         <v>565</v>
       </c>
-      <c r="D14" s="40" t="n">
+      <c r="D14" s="43" t="n">
         <v>46311.04166666666</v>
       </c>
-      <c r="E14" s="40" t="n">
+      <c r="E14" s="43" t="n">
         <v>46311.29166666666</v>
       </c>
-      <c r="F14" s="40" t="n">
+      <c r="F14" s="43" t="n">
         <v>46312.625</v>
       </c>
       <c r="G14" s="24">
@@ -1154,13 +1163,13 @@
       <c r="C15" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D15" s="40" t="n">
+      <c r="D15" s="43" t="n">
         <v>46312.75</v>
       </c>
-      <c r="E15" s="40" t="n">
+      <c r="E15" s="43" t="n">
         <v>46312.75</v>
       </c>
-      <c r="F15" s="40" t="n">
+      <c r="F15" s="43" t="n">
         <v>46313.45833333334</v>
       </c>
       <c r="G15" s="24">
@@ -1192,13 +1201,13 @@
       <c r="C16" s="23" t="n">
         <v>485</v>
       </c>
-      <c r="D16" s="40" t="n">
+      <c r="D16" s="43" t="n">
         <v>46314.95833333334</v>
       </c>
-      <c r="E16" s="40" t="n">
+      <c r="E16" s="43" t="n">
         <v>46315.375</v>
       </c>
-      <c r="F16" s="40" t="n">
+      <c r="F16" s="43" t="n">
         <v>46316.33333333334</v>
       </c>
       <c r="G16" s="24">
@@ -1230,13 +1239,13 @@
       <c r="C17" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D17" s="40" t="n">
+      <c r="D17" s="43" t="n">
         <v>46308.625</v>
       </c>
-      <c r="E17" s="40" t="n">
+      <c r="E17" s="43" t="n">
         <v>46309.25</v>
       </c>
-      <c r="F17" s="40" t="n">
+      <c r="F17" s="43" t="n">
         <v>46311.25</v>
       </c>
       <c r="G17" s="24">
@@ -1268,13 +1277,13 @@
       <c r="C18" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D18" s="40" t="n">
+      <c r="D18" s="43" t="n">
         <v>46311.95833333334</v>
       </c>
-      <c r="E18" s="40" t="n">
+      <c r="E18" s="43" t="n">
         <v>46312.33333333334</v>
       </c>
-      <c r="F18" s="40" t="n">
+      <c r="F18" s="43" t="n">
         <v>46313.29166666666</v>
       </c>
       <c r="G18" s="24">
@@ -1306,13 +1315,13 @@
       <c r="C19" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D19" s="40" t="n">
+      <c r="D19" s="43" t="n">
         <v>46313.83333333334</v>
       </c>
-      <c r="E19" s="40" t="n">
+      <c r="E19" s="43" t="n">
         <v>46313.83333333334</v>
       </c>
-      <c r="F19" s="40" t="n">
+      <c r="F19" s="43" t="n">
         <v>46315.33333333334</v>
       </c>
       <c r="G19" s="24">
@@ -1331,7 +1340,7 @@
       <c r="J19" s="23" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="34" t="inlineStr">
+      <c r="A22" s="37" t="inlineStr">
         <is>
           <t>Berth &amp; gate notices on this sheet</t>
         </is>
@@ -1364,10 +1373,10 @@
           <t>Notice / change vs previous sheet</t>
         </is>
       </c>
-      <c r="G23" s="35" t="n"/>
-      <c r="H23" s="35" t="n"/>
-      <c r="I23" s="35" t="n"/>
-      <c r="J23" s="36" t="n"/>
+      <c r="G23" s="38" t="n"/>
+      <c r="H23" s="38" t="n"/>
+      <c r="I23" s="38" t="n"/>
+      <c r="J23" s="39" t="n"/>
     </row>
     <row r="24" ht="42" customHeight="1">
       <c r="A24" s="16" t="inlineStr">
@@ -1380,7 +1389,7 @@
           <t>Berth closed</t>
         </is>
       </c>
-      <c r="C24" s="38" t="n"/>
+      <c r="C24" s="41" t="n"/>
       <c r="D24" s="17" t="inlineStr">
         <is>
           <t>–</t>
@@ -1396,10 +1405,10 @@
           <t>(no longer printed – 20D now has vessels booked and berthing)  —  Dropped from sheet: the 4–24 Oct closure notice is gone, so the vessel bookings no longer conflict</t>
         </is>
       </c>
-      <c r="G24" s="35" t="n"/>
-      <c r="H24" s="35" t="n"/>
-      <c r="I24" s="35" t="n"/>
-      <c r="J24" s="36" t="n"/>
+      <c r="G24" s="38" t="n"/>
+      <c r="H24" s="38" t="n"/>
+      <c r="I24" s="38" t="n"/>
+      <c r="J24" s="39" t="n"/>
     </row>
     <row r="25" ht="42" customHeight="1">
       <c r="A25" s="16" t="inlineStr">
@@ -1412,11 +1421,11 @@
           <t>Berth closed</t>
         </is>
       </c>
-      <c r="C25" s="38" t="n"/>
-      <c r="D25" s="41" t="n">
+      <c r="C25" s="41" t="n"/>
+      <c r="D25" s="44" t="n">
         <v>46300</v>
       </c>
-      <c r="E25" s="41" t="n">
+      <c r="E25" s="44" t="n">
         <v>46315</v>
       </c>
       <c r="F25" s="16" t="inlineStr">
@@ -1424,10 +1433,10 @@
           <t>CLOSE (Oct 5–20 2026) printed under 20E; earlier sheets said G.25 stops working 5–18 Oct to change trolley rail  —  Changed: gate stoppage 5–18 Oct became a berth CLOSE 5–20 Oct</t>
         </is>
       </c>
-      <c r="G25" s="35" t="n"/>
-      <c r="H25" s="35" t="n"/>
-      <c r="I25" s="35" t="n"/>
-      <c r="J25" s="36" t="n"/>
+      <c r="G25" s="38" t="n"/>
+      <c r="H25" s="38" t="n"/>
+      <c r="I25" s="38" t="n"/>
+      <c r="J25" s="39" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
